--- a/public/format/create_member.xlsx
+++ b/public/format/create_member.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/puskar/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B58A7FB2-F0BF-4641-94FA-36DDA28317DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97D97032-1530-404C-B305-38CEA67A2E9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4420" yWindow="660" windowWidth="24980" windowHeight="17160" xr2:uid="{5D4DE1BE-5760-6D44-A2FA-61F9C82C6372}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Father's Name</t>
   </si>
@@ -69,13 +69,19 @@
   </si>
   <si>
     <t>Legal Representative's  Citizenship Number(*)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Account Type (*) </t>
+  </si>
+  <si>
+    <t>Opening Balance (*)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -96,6 +102,12 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow (Body)"/>
     </font>
   </fonts>
   <fills count="2">
@@ -126,10 +138,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -464,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D466F43E-01AF-7F4E-ACDA-DAD9AC63F01D}">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="23.1640625" customWidth="1"/>
@@ -475,9 +485,11 @@
     <col min="9" max="9" width="46.5" customWidth="1"/>
     <col min="10" max="10" width="38.5" customWidth="1"/>
     <col min="11" max="11" width="45.1640625" customWidth="1"/>
+    <col min="12" max="12" width="33.5" customWidth="1"/>
+    <col min="13" max="13" width="35.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="32" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="32" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -502,16 +514,21 @@
       <c r="H1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3"/>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
